--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\OneDrive\Desktop\Skole\Bachelor\Transport-under-usikkerhet---Monte-Carlo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AE43CEE-88DB-4B04-A3A4-8D5B1521D864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02266B9F-6724-4B8F-BA0B-8F217B62C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rute 1 - Rotterdam" sheetId="1" r:id="rId1"/>
     <sheet name="Rute 2 - Rostock" sheetId="2" r:id="rId2"/>
-    <sheet name="Veiledning" sheetId="3" r:id="rId3"/>
+    <sheet name="Rute 3" sheetId="5" r:id="rId3"/>
+    <sheet name="Veiledning" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
   <si>
     <t>Rute 1: Karmøy → Rotterdam → Tog → Balkan</t>
   </si>
@@ -280,7 +281,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -303,11 +304,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -334,14 +355,17 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -655,13 +679,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -807,13 +831,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="s">
@@ -949,6 +973,158 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB46D44-4105-49DC-BA5F-15C3E1F38F5D}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+    </row>
+    <row r="2" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -959,11 +1135,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
